--- a/diseases/d102/2010-2014.xlsx
+++ b/diseases/d102/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>70</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>1.305154306062973</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>26</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.4847715993948186</v>
       </c>
@@ -2297,9 +2291,6 @@
       <c r="O11" t="n">
         <v>6</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.111870369091112</v>
       </c>
@@ -2989,9 +2980,6 @@
       <c r="O15" t="n">
         <v>18</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.3356111072733359</v>
       </c>
@@ -3681,9 +3669,6 @@
       <c r="O19" t="n">
         <v>63</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>1.174638875456676</v>
       </c>
@@ -4373,9 +4358,6 @@
       <c r="O23" t="n">
         <v>71</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>1.323799367578159</v>
       </c>
@@ -5065,9 +5047,6 @@
       <c r="O27" t="n">
         <v>107</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>1.99502158212483</v>
       </c>
@@ -5757,9 +5736,6 @@
       <c r="O31" t="n">
         <v>115</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>2.144182074246313</v>
       </c>
@@ -6449,9 +6425,6 @@
       <c r="O35" t="n">
         <v>105</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>1.957731459094459</v>
       </c>
@@ -7141,9 +7114,6 @@
       <c r="O39" t="n">
         <v>164</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>3.057790088490394</v>
       </c>
@@ -7833,9 +7803,6 @@
       <c r="O43" t="n">
         <v>337</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>6.283385730617456</v>
       </c>
@@ -8525,9 +8492,6 @@
       <c r="O47" t="n">
         <v>363</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>6.768157330012275</v>
       </c>
@@ -9217,9 +9181,6 @@
       <c r="O51" t="n">
         <v>183</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>3.396284613104722</v>
       </c>
@@ -9909,9 +9870,6 @@
       <c r="O55" t="n">
         <v>86</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>1.596068178836099</v>
       </c>
@@ -10601,9 +10559,6 @@
       <c r="O59" t="n">
         <v>70</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>1.299125261843336</v>
       </c>
@@ -11293,9 +11248,6 @@
       <c r="O63" t="n">
         <v>78</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>1.447596720339718</v>
       </c>
@@ -11985,9 +11937,6 @@
       <c r="O67" t="n">
         <v>193</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>3.581873936225199</v>
       </c>
@@ -12677,9 +12626,6 @@
       <c r="O71" t="n">
         <v>174</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>3.229254222296293</v>
       </c>
@@ -13369,9 +13315,6 @@
       <c r="O75" t="n">
         <v>143</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>2.653927320622816</v>
       </c>
@@ -14061,9 +14004,6 @@
       <c r="O79" t="n">
         <v>186</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>3.451961410040865</v>
       </c>
@@ -14753,9 +14693,6 @@
       <c r="O83" t="n">
         <v>152</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>2.820957711431245</v>
       </c>
@@ -15445,9 +15382,6 @@
       <c r="O87" t="n">
         <v>130</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>2.412661200566196</v>
       </c>
@@ -16137,9 +16071,6 @@
       <c r="O91" t="n">
         <v>236</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>4.379908025643248</v>
       </c>
@@ -16829,9 +16760,6 @@
       <c r="O95" t="n">
         <v>204</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>3.786022191657723</v>
       </c>
@@ -17521,9 +17449,6 @@
       <c r="O99" t="n">
         <v>155</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>2.862962983828046</v>
       </c>
@@ -18213,9 +18138,6 @@
       <c r="O103" t="n">
         <v>63</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>1.163655922459141</v>
       </c>
@@ -18905,9 +18827,6 @@
       <c r="O107" t="n">
         <v>23</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.4248267653422261</v>
       </c>
@@ -19597,9 +19516,6 @@
       <c r="O111" t="n">
         <v>19</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.3509438496305346</v>
       </c>
@@ -20289,9 +20205,6 @@
       <c r="O115" t="n">
         <v>56</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>1.034360819963681</v>
       </c>
@@ -20981,9 +20894,6 @@
       <c r="O119" t="n">
         <v>56</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>1.034360819963681</v>
       </c>
@@ -21673,9 +21583,6 @@
       <c r="O123" t="n">
         <v>79</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>1.459187585305907</v>
       </c>
@@ -22365,9 +22272,6 @@
       <c r="O127" t="n">
         <v>77</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>1.422246127450061</v>
       </c>
@@ -23057,9 +22961,6 @@
       <c r="O131" t="n">
         <v>71</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>1.311421753882524</v>
       </c>
@@ -23749,9 +23650,6 @@
       <c r="O135" t="n">
         <v>79</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>1.459187585305907</v>
       </c>
@@ -24441,9 +24339,6 @@
       <c r="O139" t="n">
         <v>78</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>1.440716856377984</v>
       </c>
@@ -25133,9 +25028,6 @@
       <c r="O143" t="n">
         <v>89</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>1.643894874585136</v>
       </c>
@@ -25973,9 +25865,6 @@
       <c r="O148" t="n">
         <v>58</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>1.06636210384418</v>
       </c>
@@ -26665,9 +26554,6 @@
       <c r="O152" t="n">
         <v>20</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.3677110702910966</v>
       </c>
@@ -27357,9 +27243,6 @@
       <c r="O156" t="n">
         <v>18</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.330939963261987</v>
       </c>
@@ -28049,9 +27932,6 @@
       <c r="O160" t="n">
         <v>13</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.2390121956892128</v>
       </c>
@@ -28741,9 +28621,6 @@
       <c r="O164" t="n">
         <v>44</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.8089643546404126</v>
       </c>
@@ -29433,9 +29310,6 @@
       <c r="O168" t="n">
         <v>53</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.974434336271406</v>
       </c>
@@ -30125,9 +29999,6 @@
       <c r="O172" t="n">
         <v>95</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>1.746627583882709</v>
       </c>
@@ -30817,9 +30688,6 @@
       <c r="O176" t="n">
         <v>141</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>2.592363045552232</v>
       </c>
@@ -31509,9 +31377,6 @@
       <c r="O180" t="n">
         <v>126</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>2.316579742833909</v>
       </c>
@@ -32201,9 +32066,6 @@
       <c r="O184" t="n">
         <v>199</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>3.658725149396412</v>
       </c>
@@ -32893,9 +32755,6 @@
       <c r="O188" t="n">
         <v>407</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>7.482920280423817</v>
       </c>
@@ -33585,9 +33444,6 @@
       <c r="O192" t="n">
         <v>542</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>9.96497000488872</v>
       </c>
@@ -34425,9 +34281,6 @@
       <c r="O197" t="n">
         <v>467</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>8.550476373221153</v>
       </c>
@@ -35117,9 +34970,6 @@
       <c r="O201" t="n">
         <v>207</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>3.790039848515586</v>
       </c>
@@ -35809,9 +35659,6 @@
       <c r="O205" t="n">
         <v>92</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>1.684462154895816</v>
       </c>
@@ -36501,9 +36348,6 @@
       <c r="O209" t="n">
         <v>96</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>1.757699639891286</v>
       </c>
@@ -37193,9 +37037,6 @@
       <c r="O213" t="n">
         <v>74</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>1.3548934724162</v>
       </c>
@@ -37885,9 +37726,6 @@
       <c r="O217" t="n">
         <v>79</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>1.446440328660538</v>
       </c>
@@ -38577,9 +38415,6 @@
       <c r="O221" t="n">
         <v>154</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>2.819643172325605</v>
       </c>
@@ -39269,9 +39104,6 @@
       <c r="O225" t="n">
         <v>214</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>3.918205447257659</v>
       </c>
@@ -39961,9 +39793,6 @@
       <c r="O229" t="n">
         <v>99</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>1.812627753637889</v>
       </c>
@@ -40653,9 +40482,6 @@
       <c r="O233" t="n">
         <v>121</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>2.215433921112975</v>
       </c>
@@ -41345,9 +41171,6 @@
       <c r="O237" t="n">
         <v>214</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>3.918205447257659</v>
       </c>
@@ -42036,9 +41859,6 @@
       </c>
       <c r="O241" t="n">
         <v>274</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
       </c>
       <c r="R241" t="n">
         <v>5.016767722189713</v>
